--- a/docs/course_schedule.xlsx
+++ b/docs/course_schedule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinchen/Dropbox/NTNU/CorpusLinguistics/NTNU_ENC2036/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinchen/Library/CloudStorage/Dropbox/NTNU/CorpusLinguistics/NTNU_ENC2036/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE4F1C62-94CC-E04C-AFE5-620980481215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B8D6A0-DFF3-4C46-A2E5-ABD66E33386F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28700" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Schedule" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>Week</t>
   </si>
@@ -85,18 +85,9 @@
     <t>Data Retrieval and Coding: Regular Expressions</t>
   </si>
   <si>
-    <t>Data Collection and Corpus Creation: HTML and Web Crawler</t>
-  </si>
-  <si>
     <t>Midterm</t>
   </si>
   <si>
-    <t>Keywords Analysis</t>
-  </si>
-  <si>
-    <t>Concordances, Frequency Lists, N-grams, Collocations</t>
-  </si>
-  <si>
     <t>Tokenization and Parts-of-speech Tagging</t>
   </si>
   <si>
@@ -112,19 +103,22 @@
     <t>Vector-space Representation</t>
   </si>
   <si>
-    <t>R Fundamentals</t>
-  </si>
-  <si>
-    <t>Chinese Text Analytics + Chinese Word Segmentation</t>
-  </si>
-  <si>
     <t>Near-Synonyms and Distcintive Collexemes</t>
   </si>
   <si>
     <t>Holiday</t>
   </si>
   <si>
-    <t>Quantitative Corpus Linguistics: A Primer</t>
+    <t>Corpys Analysis: Concordances, Frequency Lists, N-grams, Collocations</t>
+  </si>
+  <si>
+    <t>Quantitative Corpus Linguistics: A Primer; Data Collection and Corpus Creation: HTML and Web Crawler</t>
+  </si>
+  <si>
+    <t>Chinese Text Analytics (Word Segmentation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Keyword Analysis</t>
   </si>
 </sst>
 </file>
@@ -608,7 +602,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,11 +610,33 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -980,8 +996,8 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="58" customWidth="1"/>
-    <col min="4" max="4" width="38.5" customWidth="1"/>
+    <col min="3" max="3" width="80.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -994,197 +1010,206 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2">
-        <v>44610</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="6">
+        <v>46080</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2">
-        <v>44617</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="6">
+        <v>46087</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="D3" s="10"/>
+    </row>
+    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2">
-        <v>44624</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="6">
+        <v>46094</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="10"/>
+    </row>
+    <row r="5" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6">
+        <v>46101</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="6">
+        <v>46108</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="10"/>
+    </row>
+    <row r="7" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="6">
+        <v>46115</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="10"/>
+    </row>
+    <row r="8" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6">
+        <v>46122</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="6">
+        <v>46129</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>44631</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="6">
+        <v>46136</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="10"/>
+    </row>
+    <row r="11" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="6">
+        <v>46143</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="6">
+        <v>46150</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="6">
+        <v>46157</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2">
-        <v>44638</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="6">
+        <v>46164</v>
+      </c>
+      <c r="C14" s="9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2">
-        <v>44645</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2">
-        <v>44652</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2">
-        <v>44659</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2">
-        <v>44666</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2">
-        <v>44673</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="6">
+        <v>46171</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="6">
+        <v>46178</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2">
-        <v>44680</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="2">
-        <v>44687</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="2">
-        <v>44694</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="2">
-        <v>44701</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2">
-        <v>44708</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="6">
+        <v>46185</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="2">
-        <v>44715</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D17" s="10"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>

--- a/docs/course_schedule.xlsx
+++ b/docs/course_schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinchen/Library/CloudStorage/Dropbox/NTNU/CorpusLinguistics/NTNU_ENC2036/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B8D6A0-DFF3-4C46-A2E5-ABD66E33386F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12834778-0427-DB42-BBCF-881EDB519DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28700" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,9 +82,6 @@
     <t>Final Exam</t>
   </si>
   <si>
-    <t>Data Retrieval and Coding: Regular Expressions</t>
-  </si>
-  <si>
     <t>Midterm</t>
   </si>
   <si>
@@ -115,10 +112,13 @@
     <t>Quantitative Corpus Linguistics: A Primer; Data Collection and Corpus Creation: HTML and Web Crawler</t>
   </si>
   <si>
-    <t>Chinese Text Analytics (Word Segmentation)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Keyword Analysis</t>
+  </si>
+  <si>
+    <t>Data Retrieval and Coding: Regular Expressions + Guest Lecture</t>
+  </si>
+  <si>
+    <t>Chinese Text Analytics (Word Segmentation) + Guest Lecture</t>
   </si>
 </sst>
 </file>
@@ -602,7 +602,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -616,26 +616,13 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1012,204 +999,195 @@
       </c>
       <c r="D1" s="3"/>
     </row>
-    <row r="2" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="2">
         <v>46080</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2">
+        <v>46087</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>46094</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="3" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6">
-        <v>46087</v>
-      </c>
-      <c r="C3" s="9" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>46101</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>46108</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2">
+        <v>46115</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2">
+        <v>46122</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2">
+        <v>46129</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2">
+        <v>46136</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="10"/>
-    </row>
-    <row r="4" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="6">
-        <v>46094</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="10"/>
-    </row>
-    <row r="5" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6">
-        <v>46101</v>
-      </c>
-      <c r="C5" s="5" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2">
+        <v>46143</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>46150</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6">
-        <v>46108</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="10"/>
-    </row>
-    <row r="7" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6">
-        <v>46115</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="10"/>
-    </row>
-    <row r="8" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6">
-        <v>46122</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="10"/>
-    </row>
-    <row r="9" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6">
-        <v>46129</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="10"/>
-    </row>
-    <row r="10" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6">
-        <v>46136</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="10"/>
-    </row>
-    <row r="11" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="6">
-        <v>46143</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="7"/>
-    </row>
-    <row r="12" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="6">
-        <v>46150</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2">
+        <v>46157</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="7"/>
-    </row>
-    <row r="13" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="6">
-        <v>46157</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2">
+        <v>46164</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="7"/>
-    </row>
-    <row r="14" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="6">
-        <v>46164</v>
-      </c>
-      <c r="C14" s="9" t="s">
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2">
+        <v>46171</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2">
+        <v>46178</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6">
-        <v>46171</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6">
-        <v>46178</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="2">
         <v>46185</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="10"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="1"/>

--- a/docs/course_schedule.xlsx
+++ b/docs/course_schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinchen/Library/CloudStorage/Dropbox/NTNU/CorpusLinguistics/NTNU_ENC2036/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12834778-0427-DB42-BBCF-881EDB519DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F13ECD-80F9-E446-9844-1D0CD59962E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28700" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,13 +112,13 @@
     <t>Quantitative Corpus Linguistics: A Primer; Data Collection and Corpus Creation: HTML and Web Crawler</t>
   </si>
   <si>
-    <t xml:space="preserve"> Keyword Analysis</t>
-  </si>
-  <si>
     <t>Data Retrieval and Coding: Regular Expressions + Guest Lecture</t>
   </si>
   <si>
-    <t>Chinese Text Analytics (Word Segmentation) + Guest Lecture</t>
+    <t>Keyword Analysis</t>
+  </si>
+  <si>
+    <t>Chinese Processing</t>
   </si>
 </sst>
 </file>
@@ -602,7 +602,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -624,6 +624,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1052,7 +1055,7 @@
         <v>46108</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1062,8 +1065,8 @@
       <c r="B7" s="2">
         <v>46115</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>32</v>
+      <c r="C7" s="7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1073,8 +1076,8 @@
       <c r="B8" s="2">
         <v>46122</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>27</v>
+      <c r="C8" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1096,7 +1099,7 @@
         <v>46136</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1118,8 +1121,8 @@
       <c r="B12" s="2">
         <v>46150</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>22</v>
+      <c r="C12" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="D12" s="3"/>
     </row>

--- a/docs/course_schedule.xlsx
+++ b/docs/course_schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alvinchen/Library/CloudStorage/Dropbox/NTNU/CorpusLinguistics/NTNU_ENC2036/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75F13ECD-80F9-E446-9844-1D0CD59962E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7CDFE1D-1331-2B49-9E08-7D372990E26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28700" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,12 +79,6 @@
     <t>Week 16</t>
   </si>
   <si>
-    <t>Final Exam</t>
-  </si>
-  <si>
-    <t>Midterm</t>
-  </si>
-  <si>
     <t>Tokenization and Parts-of-speech Tagging</t>
   </si>
   <si>
@@ -100,9 +94,6 @@
     <t>Vector-space Representation</t>
   </si>
   <si>
-    <t>Near-Synonyms and Distcintive Collexemes</t>
-  </si>
-  <si>
     <t>Holiday</t>
   </si>
   <si>
@@ -119,6 +110,15 @@
   </si>
   <si>
     <t>Chinese Processing</t>
+  </si>
+  <si>
+    <t>Final Project Presentation (Paper Due: 6/19?)</t>
+  </si>
+  <si>
+    <t>Constructions and Idioms + Project Progress Report/Discussion</t>
+  </si>
+  <si>
+    <t>Catch-up</t>
   </si>
 </sst>
 </file>
@@ -602,7 +602,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -624,9 +624,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1010,7 +1007,7 @@
         <v>46080</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -1021,7 +1018,7 @@
         <v>46087</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -1032,7 +1029,7 @@
         <v>46094</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1043,7 +1040,7 @@
         <v>46101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3"/>
     </row>
@@ -1055,7 +1052,7 @@
         <v>46108</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -1066,7 +1063,7 @@
         <v>46115</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -1076,8 +1073,8 @@
       <c r="B8" s="2">
         <v>46122</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>31</v>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1087,8 +1084,8 @@
       <c r="B9" s="2">
         <v>46129</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>20</v>
+      <c r="C9" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -1099,7 +1096,7 @@
         <v>46136</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -1110,7 +1107,7 @@
         <v>46143</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3"/>
     </row>
@@ -1122,7 +1119,7 @@
         <v>46150</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="3"/>
     </row>
@@ -1134,7 +1131,7 @@
         <v>46157</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D13" s="3"/>
     </row>
@@ -1146,7 +1143,7 @@
         <v>46164</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="3"/>
     </row>
@@ -1158,7 +1155,7 @@
         <v>46171</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D15" s="3"/>
     </row>
@@ -1170,7 +1167,7 @@
         <v>46178</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -1182,7 +1179,7 @@
         <v>46185</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
